--- a/VerveStacks_CAN_grids/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN_grids/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28B1E722-5558-419F-A323-598EA6A5F1CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{689D58DA-A2B1-4613-96DD-F8667CFC7975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C97E164D-AE8D-4C72-997D-B2D9813AD56F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0DA943B2-7745-49F0-B635-A9E38BB32567}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,24 +81,24 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_CA24-240</t>
+  </si>
+  <si>
+    <t>e_w104561026-500</t>
+  </si>
+  <si>
+    <t>e_w614612290-500</t>
+  </si>
+  <si>
     <t>e_w166899876-500</t>
   </si>
   <si>
-    <t>e_w614612290-500</t>
+    <t>e_CA200-500</t>
   </si>
   <si>
     <t>e_w113343685-500</t>
   </si>
   <si>
-    <t>e_CA24-240</t>
-  </si>
-  <si>
-    <t>e_w104561026-500</t>
-  </si>
-  <si>
-    <t>e_CA200-500</t>
-  </si>
-  <si>
     <t>ep_bioenergy_CA24-240</t>
   </si>
   <si>
@@ -249,18 +249,18 @@
     <t>ep_coal_subcritical_</t>
   </si>
   <si>
+    <t>e_w273447830-240</t>
+  </si>
+  <si>
+    <t>e_w29999719-500</t>
+  </si>
+  <si>
     <t>e_CA229-345</t>
   </si>
   <si>
     <t>e_w269999294-345</t>
   </si>
   <si>
-    <t>e_w273447830-240</t>
-  </si>
-  <si>
-    <t>e_w29999719-500</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_CCS_G100000101026</t>
   </si>
   <si>
@@ -780,15 +780,15 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w323166651-315</t>
+  </si>
+  <si>
     <t>e_w609824151-240</t>
   </si>
   <si>
     <t>e_w323896233-735</t>
   </si>
   <si>
-    <t>e_w323166651-315</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_CA121-315</t>
   </si>
   <si>
@@ -1692,15 +1692,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_050</t>
+  </si>
+  <si>
     <t>elc_spv_051</t>
   </si>
   <si>
     <t>elc_spv_074</t>
   </si>
   <si>
-    <t>elc_spv_050</t>
-  </si>
-  <si>
     <t>ep_solar_pv_044</t>
   </si>
   <si>
@@ -1833,12 +1833,12 @@
     <t>ep_solar_pv_287</t>
   </si>
   <si>
+    <t>e_w911604497-287</t>
+  </si>
+  <si>
     <t>e_w911604499-287</t>
   </si>
   <si>
-    <t>e_w911604497-287</t>
-  </si>
-  <si>
     <t>ep_solar_pv_G100000805202</t>
   </si>
   <si>
@@ -2118,36 +2118,36 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/614612290-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/104561026-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/113343685-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - CA24-240_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - CA200-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/166899876-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/614612290-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/113343685-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/104561026-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - CA24-240_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - CA200-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant</t>
   </si>
   <si>
@@ -2193,21 +2193,21 @@
     <t>Point Aconi Generating Station_--</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Boundary Dam power station_Unit 3</t>
   </si>
   <si>
@@ -2520,12 +2520,12 @@
     <t>Aggregated Plant - IRENA Gap - way/614612290-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/609824151-240_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/323166651-315_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/609824151-240_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Abitibi Canyon hydroelectric plant_</t>
   </si>
   <si>
@@ -2919,18 +2919,18 @@
     <t>Coleson Cove power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CAN_2528_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - IRENA Gap - CAN_2163_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - CAN_2100_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CAN_2528_Missing Solar Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - CAN_2163_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Travers Solar_--</t>
   </si>
   <si>
@@ -3453,16 +3453,16 @@
     <t>ccs retrofit of -- Shand power station_Unit 1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
@@ -4133,7 +4133,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C80B766-73D9-4CE4-9CFE-BC25B2E8BB38}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49192EAE-FF2D-459C-AA15-085EC49611C0}">
   <dimension ref="B9:T154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4265,7 +4265,7 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>8.5120000000000029E-2</v>
@@ -4321,7 +4321,7 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>0.27467999999999998</v>
@@ -4377,7 +4377,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14">
         <v>9.1200000000000003E-2</v>
@@ -4433,7 +4433,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E15">
         <v>0.12960000000000002</v>
@@ -4489,7 +4489,7 @@
         <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16">
         <v>0.12960000000000002</v>
@@ -4769,7 +4769,7 @@
         <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E21">
         <v>9.1200000000000003E-2</v>
@@ -4825,7 +4825,7 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E22">
         <v>0.13770000000000002</v>
@@ -4937,7 +4937,7 @@
         <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E24">
         <v>0.13770000000000002</v>
@@ -4993,7 +4993,7 @@
         <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E25">
         <v>0.1729</v>
@@ -5049,7 +5049,7 @@
         <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26">
         <v>0.13770000000000002</v>
@@ -5105,7 +5105,7 @@
         <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E27">
         <v>0.10944000000000001</v>
@@ -5161,7 +5161,7 @@
         <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>0.10944000000000001</v>
@@ -5217,7 +5217,7 @@
         <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E29">
         <v>0.10944000000000001</v>
@@ -5609,7 +5609,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E36">
         <v>0.50749999999999995</v>
@@ -5665,7 +5665,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E37">
         <v>0.52500000000000002</v>
@@ -8689,7 +8689,7 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E91">
         <v>0.25374999999999998</v>
@@ -8745,7 +8745,7 @@
         <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E92">
         <v>0.25374999999999998</v>
@@ -11713,7 +11713,7 @@
         <v>533</v>
       </c>
       <c r="D145" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E145">
         <v>0.23624999999999999</v>
@@ -12175,7 +12175,7 @@
         <v>533</v>
       </c>
       <c r="D154" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E154">
         <v>0.23624999999999999</v>
@@ -12208,7 +12208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83898748-7BD2-4B9D-988C-3E24CA8160A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2C799D-EAA8-433C-84EF-AFB9E1E1E4BA}">
   <dimension ref="B9:T675"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12290,13 +12290,13 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.12402912621359226</v>
+        <v>0.10064077669902916</v>
       </c>
       <c r="G11">
         <v>0.33</v>
       </c>
       <c r="H11">
-        <v>4024.9999999999995</v>
+        <v>4024.9999999999991</v>
       </c>
       <c r="I11">
         <v>143</v>
@@ -12343,13 +12343,13 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>7.0873786407766995E-2</v>
+        <v>9.0718446601941768E-2</v>
       </c>
       <c r="G12">
         <v>0.33</v>
       </c>
       <c r="H12">
-        <v>4025</v>
+        <v>4024.9999999999995</v>
       </c>
       <c r="I12">
         <v>143</v>
@@ -12396,13 +12396,13 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>8.2213592233009725E-2</v>
+        <v>7.0873786407766995E-2</v>
       </c>
       <c r="G13">
         <v>0.33</v>
       </c>
       <c r="H13">
-        <v>4024.9999999999995</v>
+        <v>4025</v>
       </c>
       <c r="I13">
         <v>143</v>
@@ -12449,13 +12449,13 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.10064077669902916</v>
+        <v>0.12402912621359226</v>
       </c>
       <c r="G14">
         <v>0.33</v>
       </c>
       <c r="H14">
-        <v>4024.9999999999991</v>
+        <v>4024.9999999999995</v>
       </c>
       <c r="I14">
         <v>143</v>
@@ -12502,7 +12502,7 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>9.0718446601941768E-2</v>
+        <v>0.18923300970873791</v>
       </c>
       <c r="G15">
         <v>0.33</v>
@@ -12555,7 +12555,7 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>0.18923300970873791</v>
+        <v>8.2213592233009725E-2</v>
       </c>
       <c r="G16">
         <v>0.33</v>
@@ -12602,7 +12602,7 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E17">
         <v>1993</v>
@@ -12655,7 +12655,7 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E18">
         <v>2017</v>
@@ -12814,7 +12814,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21">
         <v>1994</v>
@@ -12867,7 +12867,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E22">
         <v>2015</v>
@@ -12920,7 +12920,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E23">
         <v>2015</v>
@@ -12973,7 +12973,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E24">
         <v>2015</v>
@@ -13026,7 +13026,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E25">
         <v>2015</v>
@@ -13185,7 +13185,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28">
         <v>2013</v>
@@ -13238,7 +13238,7 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E29">
         <v>1985</v>
@@ -13397,7 +13397,7 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>1972</v>
@@ -13450,7 +13450,7 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E33">
         <v>2015</v>
@@ -13503,7 +13503,7 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E34">
         <v>2018</v>
@@ -13609,7 +13609,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E36">
         <v>2015</v>
@@ -14669,7 +14669,7 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E56">
         <v>2010</v>
@@ -14987,25 +14987,25 @@
         <v>68</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.21728821580690957</v>
+        <v>0.42029749171793646</v>
       </c>
       <c r="G62">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H62">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="I62">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J62">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -15040,13 +15040,13 @@
         <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.1374680548982489</v>
+        <v>0.27937056318031228</v>
       </c>
       <c r="G63">
         <v>0.34</v>
@@ -15093,13 +15093,13 @@
         <v>68</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.42029749171793646</v>
+        <v>0.44477567439659244</v>
       </c>
       <c r="G64">
         <v>0.36</v>
@@ -15108,7 +15108,7 @@
         <v>2000</v>
       </c>
       <c r="I64">
-        <v>60</v>
+        <v>59.999999999999993</v>
       </c>
       <c r="J64">
         <v>5</v>
@@ -15152,7 +15152,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.27937056318031228</v>
+        <v>0.21728821580690957</v>
       </c>
       <c r="G65">
         <v>0.34</v>
@@ -15205,19 +15205,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.44477567439659244</v>
+        <v>0.1374680548982489</v>
       </c>
       <c r="G66">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H66">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="I66">
-        <v>59.999999999999993</v>
+        <v>66</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -15252,7 +15252,7 @@
         <v>68</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E67">
         <v>2014</v>
@@ -15305,7 +15305,7 @@
         <v>68</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E68">
         <v>2014</v>
@@ -15358,7 +15358,7 @@
         <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E69">
         <v>1993</v>
@@ -15411,7 +15411,7 @@
         <v>68</v>
       </c>
       <c r="D70" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E70">
         <v>1970</v>
@@ -15464,7 +15464,7 @@
         <v>68</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E71">
         <v>1973</v>
@@ -15517,7 +15517,7 @@
         <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E72">
         <v>1978</v>
@@ -15782,7 +15782,7 @@
         <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E77">
         <v>1969</v>
@@ -15835,7 +15835,7 @@
         <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E78">
         <v>1991</v>
@@ -15941,7 +15941,7 @@
         <v>68</v>
       </c>
       <c r="D80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E80">
         <v>1980</v>
@@ -15994,7 +15994,7 @@
         <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E81">
         <v>1983</v>
@@ -16047,7 +16047,7 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E82">
         <v>1992</v>
@@ -16312,7 +16312,7 @@
         <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E87">
         <v>2019</v>
@@ -16365,7 +16365,7 @@
         <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E88">
         <v>2028</v>
@@ -19227,7 +19227,7 @@
         <v>90</v>
       </c>
       <c r="D142" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E142">
         <v>2001</v>
@@ -19280,7 +19280,7 @@
         <v>90</v>
       </c>
       <c r="D143" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E143">
         <v>2001</v>
@@ -21824,7 +21824,7 @@
         <v>241</v>
       </c>
       <c r="D191" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E191">
         <v>2028</v>
@@ -21989,7 +21989,7 @@
         <v>2022</v>
       </c>
       <c r="F194">
-        <v>0.24321061426041868</v>
+        <v>0.28549896500985134</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -22042,19 +22042,19 @@
         <v>2022</v>
       </c>
       <c r="F195">
-        <v>0.52807840985609933</v>
+        <v>0.24321061426041868</v>
       </c>
       <c r="G195">
         <v>1</v>
       </c>
       <c r="H195">
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="I195">
-        <v>50</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J195">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K195">
         <v>100</v>
@@ -22095,19 +22095,19 @@
         <v>2022</v>
       </c>
       <c r="F196">
-        <v>0.28549896500985134</v>
+        <v>0.52807840985609933</v>
       </c>
       <c r="G196">
         <v>1</v>
       </c>
       <c r="H196">
-        <v>2875</v>
+        <v>2500</v>
       </c>
       <c r="I196">
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="J196">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="K196">
         <v>100</v>
@@ -22142,7 +22142,7 @@
         <v>246</v>
       </c>
       <c r="D197" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E197">
         <v>2022</v>
@@ -23043,7 +23043,7 @@
         <v>246</v>
       </c>
       <c r="D214" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E214">
         <v>2002</v>
@@ -23573,7 +23573,7 @@
         <v>246</v>
       </c>
       <c r="D224" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E224">
         <v>1971</v>
@@ -23838,7 +23838,7 @@
         <v>246</v>
       </c>
       <c r="D229" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E229">
         <v>1969</v>
@@ -24209,7 +24209,7 @@
         <v>246</v>
       </c>
       <c r="D236" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E236">
         <v>2019</v>
@@ -24262,7 +24262,7 @@
         <v>246</v>
       </c>
       <c r="D237" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E237">
         <v>1961</v>
@@ -24421,7 +24421,7 @@
         <v>246</v>
       </c>
       <c r="D240" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E240">
         <v>1975</v>
@@ -24474,7 +24474,7 @@
         <v>246</v>
       </c>
       <c r="D241" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E241">
         <v>1991</v>
@@ -25322,7 +25322,7 @@
         <v>246</v>
       </c>
       <c r="D257" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E257">
         <v>1979</v>
@@ -25587,7 +25587,7 @@
         <v>246</v>
       </c>
       <c r="D262" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E262">
         <v>1979</v>
@@ -26011,7 +26011,7 @@
         <v>246</v>
       </c>
       <c r="D270" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E270">
         <v>2015</v>
@@ -26064,7 +26064,7 @@
         <v>246</v>
       </c>
       <c r="D271" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E271">
         <v>1954</v>
@@ -27230,7 +27230,7 @@
         <v>246</v>
       </c>
       <c r="D293" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E293">
         <v>2022</v>
@@ -29403,7 +29403,7 @@
         <v>246</v>
       </c>
       <c r="D334" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E334">
         <v>1944</v>
@@ -29456,7 +29456,7 @@
         <v>246</v>
       </c>
       <c r="D335" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E335">
         <v>2007</v>
@@ -30304,7 +30304,7 @@
         <v>246</v>
       </c>
       <c r="D351" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E351">
         <v>1959</v>
@@ -31311,7 +31311,7 @@
         <v>246</v>
       </c>
       <c r="D370" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E370">
         <v>1970</v>
@@ -31523,7 +31523,7 @@
         <v>246</v>
       </c>
       <c r="D374" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E374">
         <v>1990</v>
@@ -31576,7 +31576,7 @@
         <v>246</v>
       </c>
       <c r="D375" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E375">
         <v>1977</v>
@@ -33113,7 +33113,7 @@
         <v>246</v>
       </c>
       <c r="D404" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E404">
         <v>2010</v>
@@ -33166,7 +33166,7 @@
         <v>246</v>
       </c>
       <c r="D405" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E405">
         <v>2016</v>
@@ -34226,7 +34226,7 @@
         <v>246</v>
       </c>
       <c r="D425" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E425">
         <v>1907</v>
@@ -34279,7 +34279,7 @@
         <v>246</v>
       </c>
       <c r="D426" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E426">
         <v>1924</v>
@@ -34332,7 +34332,7 @@
         <v>246</v>
       </c>
       <c r="D427" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E427">
         <v>1928</v>
@@ -34385,7 +34385,7 @@
         <v>246</v>
       </c>
       <c r="D428" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E428">
         <v>1932</v>
@@ -35816,7 +35816,7 @@
         <v>533</v>
       </c>
       <c r="D455" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E455">
         <v>2005</v>
@@ -36293,7 +36293,7 @@
         <v>533</v>
       </c>
       <c r="D464" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E464">
         <v>1960</v>
@@ -36352,16 +36352,16 @@
         <v>2022</v>
       </c>
       <c r="F465">
-        <v>0.71630847441070977</v>
+        <v>0.75390842421317117</v>
       </c>
       <c r="G465">
         <v>1</v>
       </c>
       <c r="H465">
-        <v>899.99999999999989</v>
+        <v>900</v>
       </c>
       <c r="I465">
-        <v>15.000000000000002</v>
+        <v>14.999999999999998</v>
       </c>
       <c r="J465">
         <v>0</v>
@@ -36370,7 +36370,7 @@
         <v>33</v>
       </c>
       <c r="L465">
-        <v>0.15303082838173671</v>
+        <v>0.15303082838173665</v>
       </c>
       <c r="N465" t="s">
         <v>692</v>
@@ -36408,16 +36408,16 @@
         <v>2022</v>
       </c>
       <c r="F466">
-        <v>0.71438310137611905</v>
+        <v>0.71630847441070977</v>
       </c>
       <c r="G466">
         <v>1</v>
       </c>
       <c r="H466">
-        <v>900</v>
+        <v>899.99999999999989</v>
       </c>
       <c r="I466">
-        <v>15</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="J466">
         <v>0</v>
@@ -36426,7 +36426,7 @@
         <v>33</v>
       </c>
       <c r="L466">
-        <v>0.15303082838173671</v>
+        <v>0.15303082838173665</v>
       </c>
       <c r="N466" t="s">
         <v>692</v>
@@ -36464,7 +36464,7 @@
         <v>2022</v>
       </c>
       <c r="F467">
-        <v>0.75390842421317117</v>
+        <v>0.71438310137611905</v>
       </c>
       <c r="G467">
         <v>1</v>
@@ -36473,7 +36473,7 @@
         <v>900</v>
       </c>
       <c r="I467">
-        <v>14.999999999999998</v>
+        <v>15</v>
       </c>
       <c r="J467">
         <v>0</v>
@@ -36482,7 +36482,7 @@
         <v>33</v>
       </c>
       <c r="L467">
-        <v>0.15303082838173671</v>
+        <v>0.15303082838173665</v>
       </c>
       <c r="N467" t="s">
         <v>692</v>
@@ -36682,7 +36682,7 @@
         <v>550</v>
       </c>
       <c r="D471" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E471">
         <v>2023</v>
@@ -36738,7 +36738,7 @@
         <v>550</v>
       </c>
       <c r="D472" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E472">
         <v>2028</v>
@@ -36794,7 +36794,7 @@
         <v>550</v>
       </c>
       <c r="D473" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E473">
         <v>2015</v>
@@ -36850,7 +36850,7 @@
         <v>550</v>
       </c>
       <c r="D474" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E474">
         <v>2017</v>
@@ -36906,7 +36906,7 @@
         <v>550</v>
       </c>
       <c r="D475" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E475">
         <v>2018</v>
@@ -36962,7 +36962,7 @@
         <v>550</v>
       </c>
       <c r="D476" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E476">
         <v>2020</v>
@@ -37018,7 +37018,7 @@
         <v>550</v>
       </c>
       <c r="D477" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E477">
         <v>2021</v>
@@ -37074,7 +37074,7 @@
         <v>550</v>
       </c>
       <c r="D478" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E478">
         <v>2022</v>
@@ -37130,7 +37130,7 @@
         <v>550</v>
       </c>
       <c r="D479" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E479">
         <v>2023</v>
@@ -37186,7 +37186,7 @@
         <v>550</v>
       </c>
       <c r="D480" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E480">
         <v>2024</v>
@@ -37760,7 +37760,7 @@
         <v>550</v>
       </c>
       <c r="D491" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E491">
         <v>2021</v>
@@ -38974,7 +38974,7 @@
         <v>31</v>
       </c>
       <c r="L525">
-        <v>0.15303082838173671</v>
+        <v>0.15303082838173665</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -38991,7 +38991,7 @@
         <v>2015</v>
       </c>
       <c r="F526">
-        <v>1E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G526">
         <v>1</v>
@@ -39009,7 +39009,7 @@
         <v>40</v>
       </c>
       <c r="L526">
-        <v>0.15303082838173671</v>
+        <v>0.15303082838173665</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.45">
@@ -39026,7 +39026,7 @@
         <v>2015</v>
       </c>
       <c r="F527">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G527">
         <v>1</v>
@@ -39044,7 +39044,7 @@
         <v>40</v>
       </c>
       <c r="L527">
-        <v>0.15303082838173671</v>
+        <v>0.15303082838173665</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.45">
@@ -39055,7 +39055,7 @@
         <v>550</v>
       </c>
       <c r="D528" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E528">
         <v>2022</v>
@@ -39090,7 +39090,7 @@
         <v>550</v>
       </c>
       <c r="D529" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E529">
         <v>2025</v>
@@ -41000,7 +41000,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L611">
-        <v>0.34975608431259769</v>
+        <v>0.34975608431259764</v>
       </c>
     </row>
     <row r="612" spans="2:12" x14ac:dyDescent="0.45">
@@ -41023,7 +41023,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L612">
-        <v>0.34975608431259769</v>
+        <v>0.34975608431259764</v>
       </c>
     </row>
     <row r="613" spans="2:12" x14ac:dyDescent="0.45">
@@ -41046,7 +41046,7 @@
         <v>0.33123000000000002</v>
       </c>
       <c r="L613">
-        <v>0.34975608431259769</v>
+        <v>0.34975608431259764</v>
       </c>
     </row>
     <row r="614" spans="2:12" x14ac:dyDescent="0.45">
@@ -41954,7 +41954,7 @@
         <v>603</v>
       </c>
       <c r="D653" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E653">
         <v>2007</v>
@@ -41977,7 +41977,7 @@
         <v>603</v>
       </c>
       <c r="D654" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E654">
         <v>2025</v>
@@ -42092,7 +42092,7 @@
         <v>603</v>
       </c>
       <c r="D659" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E659">
         <v>2019</v>

--- a/VerveStacks_CAN_grids/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN_grids/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{689D58DA-A2B1-4613-96DD-F8667CFC7975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{803FFE07-39DB-4059-B83C-E051451DE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{0DA943B2-7745-49F0-B635-A9E38BB32567}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F8296419-DCC7-47AB-908B-AA7AF6C8B306}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -84,15 +84,15 @@
     <t>e_CA24-240</t>
   </si>
   <si>
+    <t>e_w166899876-500</t>
+  </si>
+  <si>
+    <t>e_w614612290-500</t>
+  </si>
+  <si>
     <t>e_w104561026-500</t>
   </si>
   <si>
-    <t>e_w614612290-500</t>
-  </si>
-  <si>
-    <t>e_w166899876-500</t>
-  </si>
-  <si>
     <t>e_CA200-500</t>
   </si>
   <si>
@@ -249,18 +249,18 @@
     <t>ep_coal_subcritical_</t>
   </si>
   <si>
+    <t>e_CA229-345</t>
+  </si>
+  <si>
+    <t>e_w269999294-345</t>
+  </si>
+  <si>
     <t>e_w273447830-240</t>
   </si>
   <si>
     <t>e_w29999719-500</t>
   </si>
   <si>
-    <t>e_CA229-345</t>
-  </si>
-  <si>
-    <t>e_w269999294-345</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_CCS_G100000101026</t>
   </si>
   <si>
@@ -780,12 +780,12 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w609824151-240</t>
+  </si>
+  <si>
     <t>e_w323166651-315</t>
   </si>
   <si>
-    <t>e_w609824151-240</t>
-  </si>
-  <si>
     <t>e_w323896233-735</t>
   </si>
   <si>
@@ -1833,12 +1833,12 @@
     <t>ep_solar_pv_287</t>
   </si>
   <si>
+    <t>e_w911604499-287</t>
+  </si>
+  <si>
     <t>e_w911604497-287</t>
   </si>
   <si>
-    <t>e_w911604499-287</t>
-  </si>
-  <si>
     <t>ep_solar_pv_G100000805202</t>
   </si>
   <si>
@@ -2139,15 +2139,15 @@
     <t>Aggregated Plant - EMBER Gap - way/113343685-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/166899876-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - CA24-240_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - CA200-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/166899876-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant</t>
   </si>
   <si>
@@ -2193,15 +2193,15 @@
     <t>Point Aconi Generating Station_--</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
   </si>
   <si>
@@ -2520,12 +2520,12 @@
     <t>Aggregated Plant - IRENA Gap - way/614612290-500_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/323166651-315_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/609824151-240_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/323166651-315_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Abitibi Canyon hydroelectric plant_</t>
   </si>
   <si>
@@ -2919,18 +2919,18 @@
     <t>Coleson Cove power station_1</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CAN_2100_Missing Solar Capacity</t>
+  </si>
+  <si>
+    <t>annual</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - CAN_2528_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>annual</t>
-  </si>
-  <si>
     <t>Aggregated Plant - IRENA Gap - CAN_2163_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CAN_2100_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Travers Solar_--</t>
   </si>
   <si>
@@ -3453,19 +3453,19 @@
     <t>ccs retrofit of -- Shand power station_Unit 1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant</t>
@@ -4133,7 +4133,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49192EAE-FF2D-459C-AA15-085EC49611C0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC45C41-1237-479C-97D2-B09D808FD214}">
   <dimension ref="B9:T154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4265,7 +4265,7 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E12">
         <v>8.5120000000000029E-2</v>
@@ -4321,7 +4321,7 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E13">
         <v>0.27467999999999998</v>
@@ -4377,7 +4377,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E14">
         <v>9.1200000000000003E-2</v>
@@ -4433,7 +4433,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E15">
         <v>0.12960000000000002</v>
@@ -4489,7 +4489,7 @@
         <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E16">
         <v>0.12960000000000002</v>
@@ -4769,7 +4769,7 @@
         <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21">
         <v>9.1200000000000003E-2</v>
@@ -4825,7 +4825,7 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22">
         <v>0.13770000000000002</v>
@@ -4937,7 +4937,7 @@
         <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E24">
         <v>0.13770000000000002</v>
@@ -4993,7 +4993,7 @@
         <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E25">
         <v>0.1729</v>
@@ -5049,7 +5049,7 @@
         <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E26">
         <v>0.13770000000000002</v>
@@ -5105,7 +5105,7 @@
         <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>0.10944000000000001</v>
@@ -5161,7 +5161,7 @@
         <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E28">
         <v>0.10944000000000001</v>
@@ -5217,7 +5217,7 @@
         <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="E29">
         <v>0.10944000000000001</v>
@@ -5609,7 +5609,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E36">
         <v>0.50749999999999995</v>
@@ -5665,7 +5665,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E37">
         <v>0.52500000000000002</v>
@@ -8689,7 +8689,7 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E91">
         <v>0.25374999999999998</v>
@@ -8745,7 +8745,7 @@
         <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E92">
         <v>0.25374999999999998</v>
@@ -11713,7 +11713,7 @@
         <v>533</v>
       </c>
       <c r="D145" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E145">
         <v>0.23624999999999999</v>
@@ -12175,7 +12175,7 @@
         <v>533</v>
       </c>
       <c r="D154" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E154">
         <v>0.23624999999999999</v>
@@ -12208,7 +12208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF2C799D-EAA8-433C-84EF-AFB9E1E1E4BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB5F349-1343-4105-9A19-DD6C9293F640}">
   <dimension ref="B9:T675"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12343,7 +12343,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>9.0718446601941768E-2</v>
+        <v>0.12402912621359226</v>
       </c>
       <c r="G12">
         <v>0.33</v>
@@ -12449,7 +12449,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>0.12402912621359226</v>
+        <v>9.0718446601941768E-2</v>
       </c>
       <c r="G14">
         <v>0.33</v>
@@ -12867,7 +12867,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E22">
         <v>2015</v>
@@ -12920,7 +12920,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E23">
         <v>2015</v>
@@ -12973,7 +12973,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24">
         <v>2015</v>
@@ -13397,7 +13397,7 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32">
         <v>1972</v>
@@ -13450,7 +13450,7 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33">
         <v>2015</v>
@@ -13609,7 +13609,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E36">
         <v>2015</v>
@@ -14987,25 +14987,25 @@
         <v>68</v>
       </c>
       <c r="D62" t="s">
-        <v>23</v>
+        <v>70</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.42029749171793646</v>
+        <v>0.21728821580690957</v>
       </c>
       <c r="G62">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H62">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="I62">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J62">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -15040,13 +15040,13 @@
         <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.27937056318031228</v>
+        <v>0.1374680548982489</v>
       </c>
       <c r="G63">
         <v>0.34</v>
@@ -15093,13 +15093,13 @@
         <v>68</v>
       </c>
       <c r="D64" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.44477567439659244</v>
+        <v>0.42029749171793646</v>
       </c>
       <c r="G64">
         <v>0.36</v>
@@ -15108,7 +15108,7 @@
         <v>2000</v>
       </c>
       <c r="I64">
-        <v>59.999999999999993</v>
+        <v>60</v>
       </c>
       <c r="J64">
         <v>5</v>
@@ -15152,7 +15152,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.21728821580690957</v>
+        <v>0.27937056318031228</v>
       </c>
       <c r="G65">
         <v>0.34</v>
@@ -15205,19 +15205,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.1374680548982489</v>
+        <v>0.44477567439659244</v>
       </c>
       <c r="G66">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H66">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="I66">
-        <v>66</v>
+        <v>59.999999999999993</v>
       </c>
       <c r="J66">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -15252,7 +15252,7 @@
         <v>68</v>
       </c>
       <c r="D67" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E67">
         <v>2014</v>
@@ -15305,7 +15305,7 @@
         <v>68</v>
       </c>
       <c r="D68" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E68">
         <v>2014</v>
@@ -15358,7 +15358,7 @@
         <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E69">
         <v>1993</v>
@@ -15411,7 +15411,7 @@
         <v>68</v>
       </c>
       <c r="D70" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E70">
         <v>1970</v>
@@ -15464,7 +15464,7 @@
         <v>68</v>
       </c>
       <c r="D71" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E71">
         <v>1973</v>
@@ -15517,7 +15517,7 @@
         <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E72">
         <v>1978</v>
@@ -15782,7 +15782,7 @@
         <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E77">
         <v>1969</v>
@@ -15835,7 +15835,7 @@
         <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E78">
         <v>1991</v>
@@ -15941,7 +15941,7 @@
         <v>68</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E80">
         <v>1980</v>
@@ -15994,7 +15994,7 @@
         <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E81">
         <v>1983</v>
@@ -16047,7 +16047,7 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E82">
         <v>1992</v>
@@ -16312,7 +16312,7 @@
         <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E87">
         <v>2019</v>
@@ -16365,7 +16365,7 @@
         <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E88">
         <v>2028</v>
@@ -19227,7 +19227,7 @@
         <v>90</v>
       </c>
       <c r="D142" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E142">
         <v>2001</v>
@@ -19280,7 +19280,7 @@
         <v>90</v>
       </c>
       <c r="D143" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E143">
         <v>2001</v>
@@ -21824,7 +21824,7 @@
         <v>241</v>
       </c>
       <c r="D191" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E191">
         <v>2028</v>
@@ -21989,7 +21989,7 @@
         <v>2022</v>
       </c>
       <c r="F194">
-        <v>0.28549896500985134</v>
+        <v>0.24321061426041868</v>
       </c>
       <c r="G194">
         <v>1</v>
@@ -22036,13 +22036,13 @@
         <v>246</v>
       </c>
       <c r="D195" t="s">
-        <v>248</v>
+        <v>16</v>
       </c>
       <c r="E195">
         <v>2022</v>
       </c>
       <c r="F195">
-        <v>0.24321061426041868</v>
+        <v>0.15142806194977193</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -22051,7 +22051,7 @@
         <v>2875</v>
       </c>
       <c r="I195">
-        <v>55.000000000000007</v>
+        <v>55</v>
       </c>
       <c r="J195">
         <v>2.2000000000000002</v>
@@ -22089,25 +22089,25 @@
         <v>246</v>
       </c>
       <c r="D196" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E196">
         <v>2022</v>
       </c>
       <c r="F196">
-        <v>0.52807840985609933</v>
+        <v>0.28549896500985134</v>
       </c>
       <c r="G196">
         <v>1</v>
       </c>
       <c r="H196">
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="I196">
-        <v>50</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J196">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K196">
         <v>100</v>
@@ -22142,25 +22142,25 @@
         <v>246</v>
       </c>
       <c r="D197" t="s">
-        <v>16</v>
+        <v>249</v>
       </c>
       <c r="E197">
         <v>2022</v>
       </c>
       <c r="F197">
-        <v>0.15142806194977193</v>
+        <v>0.52807840985609933</v>
       </c>
       <c r="G197">
         <v>1</v>
       </c>
       <c r="H197">
-        <v>2875</v>
+        <v>2500</v>
       </c>
       <c r="I197">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J197">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="K197">
         <v>100</v>
@@ -23573,7 +23573,7 @@
         <v>246</v>
       </c>
       <c r="D224" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E224">
         <v>1971</v>
@@ -23838,7 +23838,7 @@
         <v>246</v>
       </c>
       <c r="D229" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E229">
         <v>1969</v>
@@ -24209,7 +24209,7 @@
         <v>246</v>
       </c>
       <c r="D236" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E236">
         <v>2019</v>
@@ -24262,7 +24262,7 @@
         <v>246</v>
       </c>
       <c r="D237" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E237">
         <v>1961</v>
@@ -27230,7 +27230,7 @@
         <v>246</v>
       </c>
       <c r="D293" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E293">
         <v>2022</v>
@@ -31311,7 +31311,7 @@
         <v>246</v>
       </c>
       <c r="D370" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E370">
         <v>1970</v>
@@ -31523,7 +31523,7 @@
         <v>246</v>
       </c>
       <c r="D374" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E374">
         <v>1990</v>
@@ -31576,7 +31576,7 @@
         <v>246</v>
       </c>
       <c r="D375" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E375">
         <v>1977</v>
@@ -33113,7 +33113,7 @@
         <v>246</v>
       </c>
       <c r="D404" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E404">
         <v>2010</v>
@@ -33166,7 +33166,7 @@
         <v>246</v>
       </c>
       <c r="D405" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E405">
         <v>2016</v>
@@ -35816,7 +35816,7 @@
         <v>533</v>
       </c>
       <c r="D455" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E455">
         <v>2005</v>
@@ -36293,7 +36293,7 @@
         <v>533</v>
       </c>
       <c r="D464" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E464">
         <v>1960</v>
@@ -36370,7 +36370,7 @@
         <v>33</v>
       </c>
       <c r="L465">
-        <v>0.15303082838173665</v>
+        <v>0.15303082838173668</v>
       </c>
       <c r="N465" t="s">
         <v>692</v>
@@ -36426,7 +36426,7 @@
         <v>33</v>
       </c>
       <c r="L466">
-        <v>0.15303082838173665</v>
+        <v>0.15303082838173668</v>
       </c>
       <c r="N466" t="s">
         <v>692</v>
@@ -36482,7 +36482,7 @@
         <v>33</v>
       </c>
       <c r="L467">
-        <v>0.15303082838173665</v>
+        <v>0.15303082838173668</v>
       </c>
       <c r="N467" t="s">
         <v>692</v>
@@ -38974,7 +38974,7 @@
         <v>31</v>
       </c>
       <c r="L525">
-        <v>0.15303082838173665</v>
+        <v>0.15303082838173668</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -38991,7 +38991,7 @@
         <v>2015</v>
       </c>
       <c r="F526">
-        <v>1.1999999999999999E-3</v>
+        <v>1E-3</v>
       </c>
       <c r="G526">
         <v>1</v>
@@ -39009,7 +39009,7 @@
         <v>40</v>
       </c>
       <c r="L526">
-        <v>0.15303082838173665</v>
+        <v>0.15303082838173668</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.45">
@@ -39026,7 +39026,7 @@
         <v>2015</v>
       </c>
       <c r="F527">
-        <v>1E-3</v>
+        <v>1.1999999999999999E-3</v>
       </c>
       <c r="G527">
         <v>1</v>
@@ -39044,7 +39044,7 @@
         <v>40</v>
       </c>
       <c r="L527">
-        <v>0.15303082838173665</v>
+        <v>0.15303082838173668</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.45">
@@ -41954,7 +41954,7 @@
         <v>603</v>
       </c>
       <c r="D653" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E653">
         <v>2007</v>
@@ -41977,7 +41977,7 @@
         <v>603</v>
       </c>
       <c r="D654" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E654">
         <v>2025</v>
@@ -42092,7 +42092,7 @@
         <v>603</v>
       </c>
       <c r="D659" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E659">
         <v>2019</v>

--- a/VerveStacks_CAN_grids/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN_grids/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN_grids\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{803FFE07-39DB-4059-B83C-E051451DE2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9726E5BB-2AFB-4DDC-BDDD-1A8062778897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F8296419-DCC7-47AB-908B-AA7AF6C8B306}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{AAD919E9-DA3D-423B-BD72-913A453064EF}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -81,24 +81,24 @@
     <t>bioenergy</t>
   </si>
   <si>
+    <t>e_w166899876-500</t>
+  </si>
+  <si>
+    <t>e_w104561026-500</t>
+  </si>
+  <si>
+    <t>e_CA200-500</t>
+  </si>
+  <si>
+    <t>e_w113343685-500</t>
+  </si>
+  <si>
     <t>e_CA24-240</t>
   </si>
   <si>
-    <t>e_w166899876-500</t>
-  </si>
-  <si>
     <t>e_w614612290-500</t>
   </si>
   <si>
-    <t>e_w104561026-500</t>
-  </si>
-  <si>
-    <t>e_CA200-500</t>
-  </si>
-  <si>
-    <t>e_w113343685-500</t>
-  </si>
-  <si>
     <t>ep_bioenergy_CA24-240</t>
   </si>
   <si>
@@ -249,18 +249,18 @@
     <t>ep_coal_subcritical_</t>
   </si>
   <si>
+    <t>e_w273447830-240</t>
+  </si>
+  <si>
+    <t>e_w29999719-500</t>
+  </si>
+  <si>
     <t>e_CA229-345</t>
   </si>
   <si>
     <t>e_w269999294-345</t>
   </si>
   <si>
-    <t>e_w273447830-240</t>
-  </si>
-  <si>
-    <t>e_w29999719-500</t>
-  </si>
-  <si>
     <t>ep_coal_subcritical_CCS_G100000101026</t>
   </si>
   <si>
@@ -780,15 +780,15 @@
     <t>hydro</t>
   </si>
   <si>
+    <t>e_w323896233-735</t>
+  </si>
+  <si>
     <t>e_w609824151-240</t>
   </si>
   <si>
     <t>e_w323166651-315</t>
   </si>
   <si>
-    <t>e_w323896233-735</t>
-  </si>
-  <si>
     <t>ep_hydro_dam_CA121-315</t>
   </si>
   <si>
@@ -1692,15 +1692,15 @@
     <t>solar</t>
   </si>
   <si>
+    <t>elc_spv_051</t>
+  </si>
+  <si>
+    <t>elc_spv_074</t>
+  </si>
+  <si>
     <t>elc_spv_050</t>
   </si>
   <si>
-    <t>elc_spv_051</t>
-  </si>
-  <si>
-    <t>elc_spv_074</t>
-  </si>
-  <si>
     <t>ep_solar_pv_044</t>
   </si>
   <si>
@@ -2118,19 +2118,28 @@
     <t>ele</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - way/166899876-500_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
+    <t>GW</t>
+  </si>
+  <si>
+    <t>TWh</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - CA24-240_Missing Bioenergy Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/614612290-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>GW</t>
-  </si>
-  <si>
-    <t>TWh</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
-    <t>yes</t>
+    <t>Aggregated Plant - EMBER Gap - CA200-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
     <t>Aggregated Plant - EMBER Gap - way/104561026-500_Missing Bioenergy Capacity</t>
@@ -2139,15 +2148,6 @@
     <t>Aggregated Plant - EMBER Gap - way/113343685-500_Missing Bioenergy Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/166899876-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - CA24-240_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - CA200-500_Missing Bioenergy Capacity</t>
-  </si>
-  <si>
     <t>Aggregated Plant</t>
   </si>
   <si>
@@ -2193,21 +2193,21 @@
     <t>Point Aconi Generating Station_--</t>
   </si>
   <si>
+    <t>Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
-  </si>
-  <si>
     <t>Boundary Dam power station_Unit 3</t>
   </si>
   <si>
@@ -2514,18 +2514,18 @@
     <t>Alberta Sundance power station_Unit 4, timepoint 2</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/323166651-315_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/323896233-735_Missing Hydro Capacity</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - way/609824151-240_Missing Hydro Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - way/614612290-500_Missing Hydro Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - way/323166651-315_Missing Hydro Capacity</t>
-  </si>
-  <si>
-    <t>Aggregated Plant - IRENA Gap - way/609824151-240_Missing Hydro Capacity</t>
-  </si>
-  <si>
     <t>Abitibi Canyon hydroelectric plant_</t>
   </si>
   <si>
@@ -2925,12 +2925,12 @@
     <t>annual</t>
   </si>
   <si>
+    <t>Aggregated Plant - IRENA Gap - CAN_2163_Missing Solar Capacity</t>
+  </si>
+  <si>
     <t>Aggregated Plant - IRENA Gap - CAN_2528_Missing Solar Capacity</t>
   </si>
   <si>
-    <t>Aggregated Plant - IRENA Gap - CAN_2163_Missing Solar Capacity</t>
-  </si>
-  <si>
     <t>Travers Solar_--</t>
   </si>
   <si>
@@ -3453,16 +3453,16 @@
     <t>ccs retrofit of -- Shand power station_Unit 1</t>
   </si>
   <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
+  </si>
+  <si>
+    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
+  </si>
+  <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/29999719-500_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - CA229-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269811579-345_Missing Coal Capacity</t>
-  </si>
-  <si>
-    <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/269999294-345_Missing Coal Capacity</t>
   </si>
   <si>
     <t>ccs retrofit of -- Aggregated Plant - EMBER Gap - way/273447830-240_Missing Coal Capacity</t>
@@ -4133,7 +4133,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDC45C41-1237-479C-97D2-B09D808FD214}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DC0E449-08F2-4368-9D0C-BF82BB5ACC8E}">
   <dimension ref="B9:T154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4265,7 +4265,7 @@
         <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E12">
         <v>8.5120000000000029E-2</v>
@@ -4321,7 +4321,7 @@
         <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E13">
         <v>0.27467999999999998</v>
@@ -4377,7 +4377,7 @@
         <v>68</v>
       </c>
       <c r="D14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E14">
         <v>9.1200000000000003E-2</v>
@@ -4433,7 +4433,7 @@
         <v>68</v>
       </c>
       <c r="D15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E15">
         <v>0.12960000000000002</v>
@@ -4489,7 +4489,7 @@
         <v>68</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16">
         <v>0.12960000000000002</v>
@@ -4769,7 +4769,7 @@
         <v>68</v>
       </c>
       <c r="D21" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E21">
         <v>9.1200000000000003E-2</v>
@@ -4825,7 +4825,7 @@
         <v>68</v>
       </c>
       <c r="D22" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E22">
         <v>0.13770000000000002</v>
@@ -4937,7 +4937,7 @@
         <v>68</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E24">
         <v>0.13770000000000002</v>
@@ -4993,7 +4993,7 @@
         <v>68</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E25">
         <v>0.1729</v>
@@ -5049,7 +5049,7 @@
         <v>68</v>
       </c>
       <c r="D26" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E26">
         <v>0.13770000000000002</v>
@@ -5105,7 +5105,7 @@
         <v>68</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E27">
         <v>0.10944000000000001</v>
@@ -5161,7 +5161,7 @@
         <v>68</v>
       </c>
       <c r="D28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>0.10944000000000001</v>
@@ -5217,7 +5217,7 @@
         <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E29">
         <v>0.10944000000000001</v>
@@ -5609,7 +5609,7 @@
         <v>90</v>
       </c>
       <c r="D36" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E36">
         <v>0.50749999999999995</v>
@@ -5665,7 +5665,7 @@
         <v>90</v>
       </c>
       <c r="D37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E37">
         <v>0.52500000000000002</v>
@@ -8689,7 +8689,7 @@
         <v>90</v>
       </c>
       <c r="D91" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E91">
         <v>0.25374999999999998</v>
@@ -8745,7 +8745,7 @@
         <v>90</v>
       </c>
       <c r="D92" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E92">
         <v>0.25374999999999998</v>
@@ -11713,7 +11713,7 @@
         <v>533</v>
       </c>
       <c r="D145" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E145">
         <v>0.23624999999999999</v>
@@ -12175,7 +12175,7 @@
         <v>533</v>
       </c>
       <c r="D154" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E154">
         <v>0.23624999999999999</v>
@@ -12208,7 +12208,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBB5F349-1343-4105-9A19-DD6C9293F640}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F308FA3E-BA79-413B-80DB-22890B77921C}">
   <dimension ref="B9:T675"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12290,13 +12290,13 @@
         <v>2022</v>
       </c>
       <c r="F11">
-        <v>0.10064077669902916</v>
+        <v>0.12402912621359226</v>
       </c>
       <c r="G11">
         <v>0.33</v>
       </c>
       <c r="H11">
-        <v>4024.9999999999991</v>
+        <v>4024.9999999999995</v>
       </c>
       <c r="I11">
         <v>143</v>
@@ -12343,7 +12343,7 @@
         <v>2022</v>
       </c>
       <c r="F12">
-        <v>0.12402912621359226</v>
+        <v>9.0718446601941768E-2</v>
       </c>
       <c r="G12">
         <v>0.33</v>
@@ -12396,13 +12396,13 @@
         <v>2022</v>
       </c>
       <c r="F13">
-        <v>7.0873786407766995E-2</v>
+        <v>0.18923300970873791</v>
       </c>
       <c r="G13">
         <v>0.33</v>
       </c>
       <c r="H13">
-        <v>4025</v>
+        <v>4024.9999999999995</v>
       </c>
       <c r="I13">
         <v>143</v>
@@ -12449,7 +12449,7 @@
         <v>2022</v>
       </c>
       <c r="F14">
-        <v>9.0718446601941768E-2</v>
+        <v>8.2213592233009725E-2</v>
       </c>
       <c r="G14">
         <v>0.33</v>
@@ -12502,13 +12502,13 @@
         <v>2022</v>
       </c>
       <c r="F15">
-        <v>0.18923300970873791</v>
+        <v>0.10064077669902916</v>
       </c>
       <c r="G15">
         <v>0.33</v>
       </c>
       <c r="H15">
-        <v>4024.9999999999995</v>
+        <v>4024.9999999999991</v>
       </c>
       <c r="I15">
         <v>143</v>
@@ -12555,13 +12555,13 @@
         <v>2022</v>
       </c>
       <c r="F16">
-        <v>8.2213592233009725E-2</v>
+        <v>7.0873786407766995E-2</v>
       </c>
       <c r="G16">
         <v>0.33</v>
       </c>
       <c r="H16">
-        <v>4024.9999999999995</v>
+        <v>4025</v>
       </c>
       <c r="I16">
         <v>143</v>
@@ -12602,7 +12602,7 @@
         <v>13</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E17">
         <v>1993</v>
@@ -12655,7 +12655,7 @@
         <v>13</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>2017</v>
@@ -12814,7 +12814,7 @@
         <v>13</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E21">
         <v>1994</v>
@@ -12867,7 +12867,7 @@
         <v>13</v>
       </c>
       <c r="D22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22">
         <v>2015</v>
@@ -12920,7 +12920,7 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E23">
         <v>2015</v>
@@ -12973,7 +12973,7 @@
         <v>13</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24">
         <v>2015</v>
@@ -13026,7 +13026,7 @@
         <v>13</v>
       </c>
       <c r="D25" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E25">
         <v>2015</v>
@@ -13185,7 +13185,7 @@
         <v>13</v>
       </c>
       <c r="D28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E28">
         <v>2013</v>
@@ -13238,7 +13238,7 @@
         <v>13</v>
       </c>
       <c r="D29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E29">
         <v>1985</v>
@@ -13397,7 +13397,7 @@
         <v>13</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E32">
         <v>1972</v>
@@ -13450,7 +13450,7 @@
         <v>13</v>
       </c>
       <c r="D33" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E33">
         <v>2015</v>
@@ -13503,7 +13503,7 @@
         <v>13</v>
       </c>
       <c r="D34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E34">
         <v>2018</v>
@@ -13609,7 +13609,7 @@
         <v>13</v>
       </c>
       <c r="D36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E36">
         <v>2015</v>
@@ -14669,7 +14669,7 @@
         <v>13</v>
       </c>
       <c r="D56" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E56">
         <v>2010</v>
@@ -14987,25 +14987,25 @@
         <v>68</v>
       </c>
       <c r="D62" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
       <c r="E62">
         <v>2022</v>
       </c>
       <c r="F62">
-        <v>0.21728821580690957</v>
+        <v>0.42029749171793646</v>
       </c>
       <c r="G62">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H62">
-        <v>2300</v>
+        <v>2000</v>
       </c>
       <c r="I62">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="J62">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="K62">
         <v>50</v>
@@ -15040,13 +15040,13 @@
         <v>68</v>
       </c>
       <c r="D63" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E63">
         <v>2022</v>
       </c>
       <c r="F63">
-        <v>0.1374680548982489</v>
+        <v>0.27937056318031228</v>
       </c>
       <c r="G63">
         <v>0.34</v>
@@ -15093,13 +15093,13 @@
         <v>68</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E64">
         <v>2022</v>
       </c>
       <c r="F64">
-        <v>0.42029749171793646</v>
+        <v>0.44477567439659244</v>
       </c>
       <c r="G64">
         <v>0.36</v>
@@ -15108,7 +15108,7 @@
         <v>2000</v>
       </c>
       <c r="I64">
-        <v>60</v>
+        <v>59.999999999999993</v>
       </c>
       <c r="J64">
         <v>5</v>
@@ -15152,7 +15152,7 @@
         <v>2022</v>
       </c>
       <c r="F65">
-        <v>0.27937056318031228</v>
+        <v>0.21728821580690957</v>
       </c>
       <c r="G65">
         <v>0.34</v>
@@ -15205,19 +15205,19 @@
         <v>2022</v>
       </c>
       <c r="F66">
-        <v>0.44477567439659244</v>
+        <v>0.1374680548982489</v>
       </c>
       <c r="G66">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="H66">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="I66">
-        <v>59.999999999999993</v>
+        <v>66</v>
       </c>
       <c r="J66">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="K66">
         <v>50</v>
@@ -15252,7 +15252,7 @@
         <v>68</v>
       </c>
       <c r="D67" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E67">
         <v>2014</v>
@@ -15305,7 +15305,7 @@
         <v>68</v>
       </c>
       <c r="D68" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E68">
         <v>2014</v>
@@ -15358,7 +15358,7 @@
         <v>68</v>
       </c>
       <c r="D69" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E69">
         <v>1993</v>
@@ -15411,7 +15411,7 @@
         <v>68</v>
       </c>
       <c r="D70" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E70">
         <v>1970</v>
@@ -15464,7 +15464,7 @@
         <v>68</v>
       </c>
       <c r="D71" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E71">
         <v>1973</v>
@@ -15517,7 +15517,7 @@
         <v>68</v>
       </c>
       <c r="D72" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E72">
         <v>1978</v>
@@ -15782,7 +15782,7 @@
         <v>68</v>
       </c>
       <c r="D77" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E77">
         <v>1969</v>
@@ -15835,7 +15835,7 @@
         <v>68</v>
       </c>
       <c r="D78" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E78">
         <v>1991</v>
@@ -15941,7 +15941,7 @@
         <v>68</v>
       </c>
       <c r="D80" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E80">
         <v>1980</v>
@@ -15994,7 +15994,7 @@
         <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E81">
         <v>1983</v>
@@ -16047,7 +16047,7 @@
         <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E82">
         <v>1992</v>
@@ -16312,7 +16312,7 @@
         <v>90</v>
       </c>
       <c r="D87" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E87">
         <v>2019</v>
@@ -16365,7 +16365,7 @@
         <v>90</v>
       </c>
       <c r="D88" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E88">
         <v>2028</v>
@@ -19227,7 +19227,7 @@
         <v>90</v>
       </c>
       <c r="D142" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E142">
         <v>2001</v>
@@ -19280,7 +19280,7 @@
         <v>90</v>
       </c>
       <c r="D143" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E143">
         <v>2001</v>
@@ -21824,7 +21824,7 @@
         <v>241</v>
       </c>
       <c r="D191" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E191">
         <v>2028</v>
@@ -21989,19 +21989,19 @@
         <v>2022</v>
       </c>
       <c r="F194">
-        <v>0.24321061426041868</v>
+        <v>0.52807840985609933</v>
       </c>
       <c r="G194">
         <v>1</v>
       </c>
       <c r="H194">
-        <v>2875</v>
+        <v>2500</v>
       </c>
       <c r="I194">
-        <v>55.000000000000007</v>
+        <v>50</v>
       </c>
       <c r="J194">
-        <v>2.2000000000000002</v>
+        <v>2</v>
       </c>
       <c r="K194">
         <v>100</v>
@@ -22036,13 +22036,13 @@
         <v>246</v>
       </c>
       <c r="D195" t="s">
-        <v>16</v>
+        <v>248</v>
       </c>
       <c r="E195">
         <v>2022</v>
       </c>
       <c r="F195">
-        <v>0.15142806194977193</v>
+        <v>0.24321061426041868</v>
       </c>
       <c r="G195">
         <v>1</v>
@@ -22051,7 +22051,7 @@
         <v>2875</v>
       </c>
       <c r="I195">
-        <v>55</v>
+        <v>55.000000000000007</v>
       </c>
       <c r="J195">
         <v>2.2000000000000002</v>
@@ -22089,7 +22089,7 @@
         <v>246</v>
       </c>
       <c r="D196" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E196">
         <v>2022</v>
@@ -22142,25 +22142,25 @@
         <v>246</v>
       </c>
       <c r="D197" t="s">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="E197">
         <v>2022</v>
       </c>
       <c r="F197">
-        <v>0.52807840985609933</v>
+        <v>0.15142806194977193</v>
       </c>
       <c r="G197">
         <v>1</v>
       </c>
       <c r="H197">
-        <v>2500</v>
+        <v>2875</v>
       </c>
       <c r="I197">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J197">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="K197">
         <v>100</v>
@@ -23043,7 +23043,7 @@
         <v>246</v>
       </c>
       <c r="D214" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E214">
         <v>2002</v>
@@ -23573,7 +23573,7 @@
         <v>246</v>
       </c>
       <c r="D224" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E224">
         <v>1971</v>
@@ -23838,7 +23838,7 @@
         <v>246</v>
       </c>
       <c r="D229" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E229">
         <v>1969</v>
@@ -24209,7 +24209,7 @@
         <v>246</v>
       </c>
       <c r="D236" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E236">
         <v>2019</v>
@@ -24262,7 +24262,7 @@
         <v>246</v>
       </c>
       <c r="D237" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E237">
         <v>1961</v>
@@ -24421,7 +24421,7 @@
         <v>246</v>
       </c>
       <c r="D240" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E240">
         <v>1975</v>
@@ -24474,7 +24474,7 @@
         <v>246</v>
       </c>
       <c r="D241" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E241">
         <v>1991</v>
@@ -25322,7 +25322,7 @@
         <v>246</v>
       </c>
       <c r="D257" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E257">
         <v>1979</v>
@@ -25587,7 +25587,7 @@
         <v>246</v>
       </c>
       <c r="D262" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E262">
         <v>1979</v>
@@ -26011,7 +26011,7 @@
         <v>246</v>
       </c>
       <c r="D270" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E270">
         <v>2015</v>
@@ -26064,7 +26064,7 @@
         <v>246</v>
       </c>
       <c r="D271" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E271">
         <v>1954</v>
@@ -27230,7 +27230,7 @@
         <v>246</v>
       </c>
       <c r="D293" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E293">
         <v>2022</v>
@@ -29403,7 +29403,7 @@
         <v>246</v>
       </c>
       <c r="D334" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E334">
         <v>1944</v>
@@ -29456,7 +29456,7 @@
         <v>246</v>
       </c>
       <c r="D335" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E335">
         <v>2007</v>
@@ -30304,7 +30304,7 @@
         <v>246</v>
       </c>
       <c r="D351" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E351">
         <v>1959</v>
@@ -31311,7 +31311,7 @@
         <v>246</v>
       </c>
       <c r="D370" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E370">
         <v>1970</v>
@@ -31523,7 +31523,7 @@
         <v>246</v>
       </c>
       <c r="D374" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E374">
         <v>1990</v>
@@ -31576,7 +31576,7 @@
         <v>246</v>
       </c>
       <c r="D375" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E375">
         <v>1977</v>
@@ -33113,7 +33113,7 @@
         <v>246</v>
       </c>
       <c r="D404" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E404">
         <v>2010</v>
@@ -33166,7 +33166,7 @@
         <v>246</v>
       </c>
       <c r="D405" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E405">
         <v>2016</v>
@@ -34226,7 +34226,7 @@
         <v>246</v>
       </c>
       <c r="D425" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E425">
         <v>1907</v>
@@ -34279,7 +34279,7 @@
         <v>246</v>
       </c>
       <c r="D426" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E426">
         <v>1924</v>
@@ -34332,7 +34332,7 @@
         <v>246</v>
       </c>
       <c r="D427" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E427">
         <v>1928</v>
@@ -34385,7 +34385,7 @@
         <v>246</v>
       </c>
       <c r="D428" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E428">
         <v>1932</v>
@@ -35816,7 +35816,7 @@
         <v>533</v>
       </c>
       <c r="D455" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E455">
         <v>2005</v>
@@ -36293,7 +36293,7 @@
         <v>533</v>
       </c>
       <c r="D464" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E464">
         <v>1960</v>
@@ -36352,16 +36352,16 @@
         <v>2022</v>
       </c>
       <c r="F465">
-        <v>0.75390842421317117</v>
+        <v>0.71630847441070977</v>
       </c>
       <c r="G465">
         <v>1</v>
       </c>
       <c r="H465">
-        <v>900</v>
+        <v>899.99999999999989</v>
       </c>
       <c r="I465">
-        <v>14.999999999999998</v>
+        <v>15.000000000000002</v>
       </c>
       <c r="J465">
         <v>0</v>
@@ -36370,7 +36370,7 @@
         <v>33</v>
       </c>
       <c r="L465">
-        <v>0.15303082838173668</v>
+        <v>0.15303082838173671</v>
       </c>
       <c r="N465" t="s">
         <v>692</v>
@@ -36408,16 +36408,16 @@
         <v>2022</v>
       </c>
       <c r="F466">
-        <v>0.71630847441070977</v>
+        <v>0.71438310137611905</v>
       </c>
       <c r="G466">
         <v>1</v>
       </c>
       <c r="H466">
-        <v>899.99999999999989</v>
+        <v>900</v>
       </c>
       <c r="I466">
-        <v>15.000000000000002</v>
+        <v>15</v>
       </c>
       <c r="J466">
         <v>0</v>
@@ -36426,7 +36426,7 @@
         <v>33</v>
       </c>
       <c r="L466">
-        <v>0.15303082838173668</v>
+        <v>0.15303082838173671</v>
       </c>
       <c r="N466" t="s">
         <v>692</v>
@@ -36464,7 +36464,7 @@
         <v>2022</v>
       </c>
       <c r="F467">
-        <v>0.71438310137611905</v>
+        <v>0.75390842421317117</v>
       </c>
       <c r="G467">
         <v>1</v>
@@ -36473,7 +36473,7 @@
         <v>900</v>
       </c>
       <c r="I467">
-        <v>15</v>
+        <v>14.999999999999998</v>
       </c>
       <c r="J467">
         <v>0</v>
@@ -36482,7 +36482,7 @@
         <v>33</v>
       </c>
       <c r="L467">
-        <v>0.15303082838173668</v>
+        <v>0.15303082838173671</v>
       </c>
       <c r="N467" t="s">
         <v>692</v>
@@ -36682,7 +36682,7 @@
         <v>550</v>
       </c>
       <c r="D471" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E471">
         <v>2023</v>
@@ -36738,7 +36738,7 @@
         <v>550</v>
       </c>
       <c r="D472" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="E472">
         <v>2028</v>
@@ -36794,7 +36794,7 @@
         <v>550</v>
       </c>
       <c r="D473" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E473">
         <v>2015</v>
@@ -36850,7 +36850,7 @@
         <v>550</v>
       </c>
       <c r="D474" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E474">
         <v>2017</v>
@@ -36906,7 +36906,7 @@
         <v>550</v>
       </c>
       <c r="D475" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E475">
         <v>2018</v>
@@ -36962,7 +36962,7 @@
         <v>550</v>
       </c>
       <c r="D476" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E476">
         <v>2020</v>
@@ -37018,7 +37018,7 @@
         <v>550</v>
       </c>
       <c r="D477" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E477">
         <v>2021</v>
@@ -37074,7 +37074,7 @@
         <v>550</v>
       </c>
       <c r="D478" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E478">
         <v>2022</v>
@@ -37130,7 +37130,7 @@
         <v>550</v>
       </c>
       <c r="D479" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E479">
         <v>2023</v>
@@ -37186,7 +37186,7 @@
         <v>550</v>
       </c>
       <c r="D480" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E480">
         <v>2024</v>
@@ -37760,7 +37760,7 @@
         <v>550</v>
       </c>
       <c r="D491" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E491">
         <v>2021</v>
@@ -38974,7 +38974,7 @@
         <v>31</v>
       </c>
       <c r="L525">
-        <v>0.15303082838173668</v>
+        <v>0.15303082838173671</v>
       </c>
     </row>
     <row r="526" spans="2:12" x14ac:dyDescent="0.45">
@@ -39009,7 +39009,7 @@
         <v>40</v>
       </c>
       <c r="L526">
-        <v>0.15303082838173668</v>
+        <v>0.15303082838173671</v>
       </c>
     </row>
     <row r="527" spans="2:12" x14ac:dyDescent="0.45">
@@ -39044,7 +39044,7 @@
         <v>40</v>
       </c>
       <c r="L527">
-        <v>0.15303082838173668</v>
+        <v>0.15303082838173671</v>
       </c>
     </row>
     <row r="528" spans="2:12" x14ac:dyDescent="0.45">
@@ -39055,7 +39055,7 @@
         <v>550</v>
       </c>
       <c r="D528" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E528">
         <v>2022</v>
@@ -39090,7 +39090,7 @@
         <v>550</v>
       </c>
       <c r="D529" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E529">
         <v>2025</v>
@@ -41954,7 +41954,7 @@
         <v>603</v>
       </c>
       <c r="D653" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E653">
         <v>2007</v>
@@ -41977,7 +41977,7 @@
         <v>603</v>
       </c>
       <c r="D654" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E654">
         <v>2025</v>
@@ -42092,7 +42092,7 @@
         <v>603</v>
       </c>
       <c r="D659" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E659">
         <v>2019</v>
